--- a/bills/-5230747991/a40c9761a822e551b52780ea3297aa138e0778d16e784a7783c735ba3b3a2947/bill-all.xlsx
+++ b/bills/-5230747991/a40c9761a822e551b52780ea3297aa138e0778d16e784a7783c735ba3b3a2947/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/09 18:35:23</t>
+          <t>06/22 20:26:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11111.11</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/26 19:34:04</t>
+          <t>06/09 18:35:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1111.11</t>
+          <t>11111.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/26 19:33:27</t>
+          <t>05/26 19:34:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/26 19:32:08</t>
+          <t>05/26 19:33:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/26 19:30:49</t>
+          <t>05/26 19:32:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/26 01:28:11</t>
+          <t>05/26 19:30:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>116.28</t>
+          <t>1111.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/26 01:01:50</t>
+          <t>05/26 01:28:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>258.22</t>
+          <t>116.28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/26 01:01:46</t>
+          <t>05/26 01:01:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>258.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/26 00:57:35</t>
+          <t>05/26 01:01:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/26 00:57:31</t>
+          <t>05/26 00:57:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/26 00:53:28</t>
+          <t>05/26 00:57:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05/26 00:24:04</t>
+          <t>05/26 00:53:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-555.56</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05/26 00:23:43</t>
+          <t>05/26 00:24:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-10000</t>
+          <t>-1000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-1111.11</t>
+          <t>-555.56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05/26 00:23:37</t>
+          <t>05/26 00:23:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>-10000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-111.11</t>
+          <t>-1111.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05/26 00:23:34</t>
+          <t>05/26 00:23:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05/26 00:23:29</t>
+          <t>05/26 00:23:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05/26 00:23:18</t>
+          <t>05/26 00:23:29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05/26 00:04:16</t>
+          <t>05/26 00:23:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>-1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1282.05</t>
+          <t>-111.11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/26 00:04:08</t>
+          <t>05/26 00:04:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05/26 00:03:13</t>
+          <t>05/26 00:04:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1111.11</t>
+          <t>1282.05</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05/26 00:03:10</t>
+          <t>05/26 00:03:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05/26 00:03:08</t>
+          <t>05/26 00:03:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05/26 00:03:06</t>
+          <t>05/26 00:03:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05/26 00:03:04</t>
+          <t>05/26 00:03:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05/26 00:02:31</t>
+          <t>05/26 00:03:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1472.75</t>
+          <t>1111.11</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05/26 00:02:25</t>
+          <t>05/26 00:02:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05/25 23:54:28</t>
+          <t>05/26 00:02:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05/25 23:54:22</t>
+          <t>05/25 23:54:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05/25 23:46:46</t>
+          <t>05/25 23:54:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05/25 23:46:38</t>
+          <t>05/25 23:46:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05/25 23:42:30</t>
+          <t>05/25 23:46:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05/25 23:42:11</t>
+          <t>05/25 23:42:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1413.84</t>
+          <t>1472.75</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05/25 23:40:08</t>
+          <t>05/25 23:42:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05/25 23:35:35</t>
+          <t>05/25 23:40:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1503,32 +1503,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05/25 16:08:38</t>
+          <t>05/25 23:35:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>1413.84</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05/25 16:05:12</t>
+          <t>05/25 16:08:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05/25 16:02:46</t>
+          <t>05/25 16:05:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05/25 15:59:27</t>
+          <t>05/25 16:02:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>张三</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05/25 15:54:41</t>
+          <t>05/25 15:59:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,250 +1713,265 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>05/25 15:54:41</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>05/25 15:54:01</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>代付</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>05/26 00:19:22</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>汇率</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>结算</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>05/26 00:19:22</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>05/26 00:13:11</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>05/26 00:57:57</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>05/26 00:53:03</t>
+          <t>05/26 00:57:57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1978,7 +1993,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05/26 00:25:07</t>
+          <t>05/26 00:53:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2005,12 +2020,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05/26 00:24:44</t>
+          <t>05/26 00:25:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-1000</t>
+          <t>111.11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2032,12 +2047,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05/26 00:24:37</t>
+          <t>05/26 00:24:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>-1000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2059,12 +2074,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>05/26 00:24:31</t>
+          <t>05/26 00:24:37</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2086,12 +2101,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>05/26 00:03:40</t>
+          <t>05/26 00:24:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2113,7 +2128,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>05/26 00:03:30</t>
+          <t>05/26 00:03:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2140,12 +2155,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>05/26 00:03:19</t>
+          <t>05/26 00:03:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2167,12 +2182,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>05/25 16:15:02</t>
+          <t>05/26 00:03:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2194,7 +2209,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>05/25 16:13:12</t>
+          <t>05/25 16:15:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2221,7 +2236,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05/25 16:13:02</t>
+          <t>05/25 16:13:12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2248,7 +2263,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05/25 16:12:43</t>
+          <t>05/25 16:13:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2275,83 +2290,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>05/25 16:12:43</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>05/25 15:54:47</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>290924</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25889.93</t>
+          <t>291924</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4062.22</t>
+          <t>26001.04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4062.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>21827.71</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>21938.82</t>
         </is>
       </c>
     </row>
